--- a/artfynd/A 37273-2024 artfynd.xlsx
+++ b/artfynd/A 37273-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,8 +783,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96619852</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 37273-2024 artfynd.xlsx
+++ b/artfynd/A 37273-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,9 +789,766 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135813831</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58703</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nodsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>705766</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6625574</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Frötuna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>NVI Nodsta Norrtälje 2026</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135813831</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135813839</v>
+      </c>
+      <c r="B4" t="n">
+        <v>43229</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>201028</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Thymelicus lineola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ochsenheimer, 1808)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nodsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>705568</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6625611</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Frötuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>NVI Nodsta Norrtälje 2026</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135813839</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135813834</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43388</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>201075</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Boloria selene</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nodsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>705707</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6625573</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Frötuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>NVI Nodsta Norrtälje 2026</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135813834</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135813835</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43319</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>201146</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Silverblåvinge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Polyommatus amandus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nodsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>705711</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6625566</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Frötuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>NVI Nodsta Norrtälje 2026</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135813835</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135813827</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nodsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>705725</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6625539</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Frötuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>NVI Nodsta Norrtälje 2026</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135813827</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135813830</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nodsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>705788</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6625510</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Frötuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>NVI Nodsta Norrtälje 2026</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135813830</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135813841</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99551</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nodsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>705573</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6625609</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Frötuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>NVI Nodsta Norrtälje 2026</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135813841</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37273-2024 artfynd.xlsx
+++ b/artfynd/A 37273-2024 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>135813827</v>
       </c>
       <c r="B7" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>135813830</v>
       </c>
       <c r="B8" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>135813841</v>
       </c>
       <c r="B9" t="n">
-        <v>99551</v>
+        <v>99553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37273-2024 artfynd.xlsx
+++ b/artfynd/A 37273-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135813831</v>
       </c>
       <c r="B3" t="n">
-        <v>58703</v>
+        <v>58705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135813839</v>
       </c>
       <c r="B4" t="n">
-        <v>43229</v>
+        <v>43231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135813834</v>
       </c>
       <c r="B5" t="n">
-        <v>43388</v>
+        <v>43390</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>135813835</v>
       </c>
       <c r="B6" t="n">
-        <v>43319</v>
+        <v>43321</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>135813827</v>
       </c>
       <c r="B7" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>135813830</v>
       </c>
       <c r="B8" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>135813841</v>
       </c>
       <c r="B9" t="n">
-        <v>99553</v>
+        <v>99570</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37273-2024 artfynd.xlsx
+++ b/artfynd/A 37273-2024 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>135813827</v>
       </c>
       <c r="B7" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>135813830</v>
       </c>
       <c r="B8" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>135813841</v>
       </c>
       <c r="B9" t="n">
-        <v>99570</v>
+        <v>99571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37273-2024 artfynd.xlsx
+++ b/artfynd/A 37273-2024 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>135813827</v>
       </c>
       <c r="B7" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>135813830</v>
       </c>
       <c r="B8" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>135813841</v>
       </c>
       <c r="B9" t="n">
-        <v>99571</v>
+        <v>99572</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37273-2024 artfynd.xlsx
+++ b/artfynd/A 37273-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135813831</v>
       </c>
       <c r="B3" t="n">
-        <v>58705</v>
+        <v>58706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135813839</v>
       </c>
       <c r="B4" t="n">
-        <v>43231</v>
+        <v>43232</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135813834</v>
       </c>
       <c r="B5" t="n">
-        <v>43390</v>
+        <v>43391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>135813835</v>
       </c>
       <c r="B6" t="n">
-        <v>43321</v>
+        <v>43322</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>135813827</v>
       </c>
       <c r="B7" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>135813830</v>
       </c>
       <c r="B8" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>135813841</v>
       </c>
       <c r="B9" t="n">
-        <v>99572</v>
+        <v>99573</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37273-2024 artfynd.xlsx
+++ b/artfynd/A 37273-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135813831</v>
       </c>
       <c r="B3" t="n">
-        <v>58706</v>
+        <v>58710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>135813827</v>
       </c>
       <c r="B7" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>135813830</v>
       </c>
       <c r="B8" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>135813841</v>
       </c>
       <c r="B9" t="n">
-        <v>99573</v>
+        <v>99579</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37273-2024 artfynd.xlsx
+++ b/artfynd/A 37273-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135813831</v>
       </c>
       <c r="B3" t="n">
-        <v>58710</v>
+        <v>58711</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>135813827</v>
       </c>
       <c r="B7" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>135813830</v>
       </c>
       <c r="B8" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>135813841</v>
       </c>
       <c r="B9" t="n">
-        <v>99579</v>
+        <v>99580</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37273-2024 artfynd.xlsx
+++ b/artfynd/A 37273-2024 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>135813827</v>
       </c>
       <c r="B7" t="n">
-        <v>99220</v>
+        <v>99231</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>135813830</v>
       </c>
       <c r="B8" t="n">
-        <v>99220</v>
+        <v>99231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>135813841</v>
       </c>
       <c r="B9" t="n">
-        <v>99580</v>
+        <v>99591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37273-2024 artfynd.xlsx
+++ b/artfynd/A 37273-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135813831</v>
       </c>
       <c r="B3" t="n">
-        <v>58711</v>
+        <v>58716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135813839</v>
       </c>
       <c r="B4" t="n">
-        <v>43232</v>
+        <v>43237</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135813834</v>
       </c>
       <c r="B5" t="n">
-        <v>43391</v>
+        <v>43396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>135813835</v>
       </c>
       <c r="B6" t="n">
-        <v>43322</v>
+        <v>43327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>135813827</v>
       </c>
       <c r="B7" t="n">
-        <v>99231</v>
+        <v>99244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>135813830</v>
       </c>
       <c r="B8" t="n">
-        <v>99231</v>
+        <v>99244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>135813841</v>
       </c>
       <c r="B9" t="n">
-        <v>99591</v>
+        <v>99604</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37273-2024 artfynd.xlsx
+++ b/artfynd/A 37273-2024 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>135813827</v>
       </c>
       <c r="B7" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>135813830</v>
       </c>
       <c r="B8" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>135813841</v>
       </c>
       <c r="B9" t="n">
-        <v>99604</v>
+        <v>99605</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37273-2024 artfynd.xlsx
+++ b/artfynd/A 37273-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135813831</v>
       </c>
       <c r="B3" t="n">
-        <v>58716</v>
+        <v>58729</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135813839</v>
       </c>
       <c r="B4" t="n">
-        <v>43237</v>
+        <v>43250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135813834</v>
       </c>
       <c r="B5" t="n">
-        <v>43396</v>
+        <v>43409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>135813835</v>
       </c>
       <c r="B6" t="n">
-        <v>43327</v>
+        <v>43340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>135813827</v>
       </c>
       <c r="B7" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>135813830</v>
       </c>
       <c r="B8" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>135813841</v>
       </c>
       <c r="B9" t="n">
-        <v>99605</v>
+        <v>99618</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
